--- a/exports/KOTAKBANK_full_report.xlsx
+++ b/exports/KOTAKBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.38</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>379.4</v>
+        <v>367.6</v>
       </c>
       <c r="I2" t="n">
         <v>373.34882222</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.29</v>
+        <v>-5.33</v>
       </c>
       <c r="L2" t="n">
-        <v>4.74</v>
+        <v>5.69</v>
       </c>
       <c r="M2" t="n">
         <v>1.35</v>
       </c>
       <c r="N2" t="n">
-        <v>1.62</v>
+        <v>3.82</v>
       </c>
       <c r="O2" t="n">
         <v>2.28</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.8</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>377.6</v>
+        <v>387.7</v>
       </c>
       <c r="I3" t="n">
         <v>384.5794179487123</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.72</v>
+        <v>-5.47</v>
       </c>
       <c r="L3" t="n">
         <v>6.42</v>
@@ -612,7 +647,7 @@
         <v>1.51</v>
       </c>
       <c r="N3" t="n">
-        <v>2.33</v>
+        <v>2.97</v>
       </c>
       <c r="O3" t="n">
         <v>-3.82</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44599.55208333334</v>
+        <v>44600.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>365.6</v>
+        <v>359.8</v>
       </c>
       <c r="I4" t="n">
         <v>360.5626645740668</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.7</v>
+        <v>-7.2</v>
       </c>
       <c r="L4" t="n">
-        <v>6.11</v>
+        <v>7.48</v>
       </c>
       <c r="M4" t="n">
         <v>1.8</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>7.97</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44614.55208333334</v>
+        <v>44615.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>368</v>
+        <v>380.3</v>
       </c>
       <c r="I5" t="n">
         <v>373.9610259308305</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.28</v>
+        <v>-5.7</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>5.89</v>
       </c>
       <c r="M5" t="n">
         <v>1.13</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7.08</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44623.55208333334</v>
+        <v>44624.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>358.4</v>
+        <v>354</v>
       </c>
       <c r="I6" t="n">
         <v>356.5110814851987</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.76</v>
+        <v>-6.92</v>
       </c>
       <c r="L6" t="n">
-        <v>6.78</v>
+        <v>8.84</v>
       </c>
       <c r="M6" t="n">
         <v>2.52</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>6.68</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44655.38541666666</v>
+        <v>44655.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>361.9</v>
+        <v>366.9</v>
       </c>
       <c r="I7" t="n">
         <v>362.2046960598603</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.23</v>
+        <v>-3.64</v>
       </c>
       <c r="L7" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="M7" t="n">
         <v>3.09</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>5.54</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>347.2</v>
+        <v>340.5</v>
       </c>
       <c r="I8" t="n">
         <v>346.8759219433268</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.37</v>
+        <v>-7.2</v>
       </c>
       <c r="L8" t="n">
-        <v>5.7</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>0.95</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>6.98</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44679.55208333334</v>
+        <v>44680.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>353.4</v>
+        <v>360.8</v>
       </c>
       <c r="I9" t="n">
         <v>359.8752221874459</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.79</v>
+        <v>-5.96</v>
       </c>
       <c r="L9" t="n">
-        <v>4.17</v>
+        <v>6.17</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.32</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44712.38541666666</v>
+        <v>44712.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>374.4</v>
+        <v>367.4</v>
       </c>
       <c r="I10" t="n">
         <v>370.1479275009301</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>3.77</v>
+        <v>1.83</v>
       </c>
       <c r="L10" t="n">
         <v>3.38</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.24</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44748.55208333334</v>
+        <v>44749.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>341.8</v>
+        <v>345.9</v>
       </c>
       <c r="I11" t="n">
         <v>344.8017144238752</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K11" t="n">
-        <v>6.97</v>
+        <v>5.85</v>
       </c>
       <c r="L11" t="n">
         <v>3.21</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>4.83</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44767.55208333334</v>
+        <v>44768.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>359.2</v>
+        <v>354</v>
       </c>
       <c r="I12" t="n">
         <v>354.8559956453646</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>2.34</v>
       </c>
       <c r="L12" t="n">
         <v>0.98</v>
@@ -1125,7 +1268,7 @@
         <v>0.89</v>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>2.39</v>
       </c>
       <c r="O12" t="n">
         <v>1.96</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.2</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44771.55208333334</v>
+        <v>44774.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>362.8</v>
+        <v>367.4</v>
       </c>
       <c r="I13" t="n">
         <v>365.8592619480946</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.49</v>
+        <v>-3.79</v>
       </c>
       <c r="L13" t="n">
         <v>4.92</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>5.32</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>374.4</v>
+        <v>364.3</v>
       </c>
       <c r="I14" t="n">
         <v>365.4278657298506</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K14" t="n">
-        <v>1.91</v>
+        <v>-0.84</v>
       </c>
       <c r="L14" t="n">
         <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>0.24</v>
+        <v>2.4</v>
       </c>
       <c r="N14" t="n">
         <v>2.04</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.14</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44805.55208333334</v>
+        <v>44806.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>381.8</v>
+        <v>384.4</v>
       </c>
       <c r="I15" t="n">
         <v>382.9161472946451</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.8</v>
+        <v>-5.52</v>
       </c>
       <c r="L15" t="n">
         <v>5.79</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>5.7</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>379.5</v>
+        <v>370.2</v>
       </c>
       <c r="I16" t="n">
         <v>374.5313074795956</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.27</v>
+        <v>-3.69</v>
       </c>
       <c r="L16" t="n">
-        <v>2.13</v>
+        <v>4.11</v>
       </c>
       <c r="M16" t="n">
         <v>1.66</v>
       </c>
       <c r="N16" t="n">
-        <v>1.02</v>
+        <v>2.03</v>
       </c>
       <c r="O16" t="n">
         <v>0.58</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.08</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44851.38541666666</v>
+        <v>44851.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>370.8</v>
+        <v>372.2</v>
       </c>
       <c r="I17" t="n">
         <v>371.7524409000272</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.16</v>
+        <v>-0.54</v>
       </c>
       <c r="L17" t="n">
         <v>1.84</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.64</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44902.55208333334</v>
+        <v>44903.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>382.8</v>
+        <v>378</v>
       </c>
       <c r="I18" t="n">
         <v>379.4754598066481</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>51</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K18" t="n">
-        <v>2.85</v>
+        <v>1.56</v>
       </c>
       <c r="L18" t="n">
         <v>1.02</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>3.17</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>345</v>
+        <v>356.1</v>
       </c>
       <c r="I19" t="n">
         <v>355.7391252920615</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K19" t="n">
-        <v>8.73</v>
+        <v>5.79</v>
       </c>
       <c r="L19" t="n">
         <v>1.4</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.75</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44977.38541666666</v>
+        <v>44977.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>348</v>
+        <v>347.4</v>
       </c>
       <c r="I20" t="n">
         <v>347.6825124001114</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.27</v>
+        <v>-2.44</v>
       </c>
       <c r="L20" t="n">
         <v>3.4</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>3.58</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45014.38541666666</v>
+        <v>45014.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>341.8</v>
+        <v>344.9</v>
       </c>
       <c r="I21" t="n">
         <v>342.7680952655496</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>36.83333333333334</v>
+        <v>37</v>
       </c>
       <c r="K21" t="n">
-        <v>1.61</v>
+        <v>0.72</v>
       </c>
       <c r="L21" t="n">
         <v>1.58</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>3.99</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45062.55208333334</v>
+        <v>45063.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>388.4</v>
+        <v>380</v>
       </c>
       <c r="I22" t="n">
         <v>381.9049962100019</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>12.61</v>
+        <v>10.18</v>
       </c>
       <c r="L22" t="n">
         <v>0.96</v>
@@ -1695,7 +1958,7 @@
         <v>0.78</v>
       </c>
       <c r="N22" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
         <v>1.53</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>5.2</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45075.55208333334</v>
+        <v>45076.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>390.7</v>
+        <v>394.6</v>
       </c>
       <c r="I23" t="n">
         <v>394.0934381794604</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.82</v>
+        <v>-3.84</v>
       </c>
       <c r="L23" t="n">
-        <v>3.87</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="O23" t="n">
         <v>-1.7</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>3.7</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45084.55208333334</v>
+        <v>45085.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>387.9</v>
+        <v>381.8</v>
       </c>
       <c r="I24" t="n">
         <v>384.41934931068</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.7</v>
+        <v>-3.24</v>
       </c>
       <c r="L24" t="n">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
       <c r="M24" t="n">
         <v>2.16</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.71</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45117.55208333334</v>
+        <v>45118.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>374</v>
+        <v>376.5</v>
       </c>
       <c r="I25" t="n">
         <v>375.5776531048755</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K25" t="n">
-        <v>2.04</v>
+        <v>1.39</v>
       </c>
       <c r="L25" t="n">
         <v>1.47</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>2.86</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45131.38541666666</v>
+        <v>45131.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="I26" t="n">
         <v>380.2239811251379</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2</v>
+        <v>0.66</v>
       </c>
       <c r="L26" t="n">
         <v>1.2</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.64</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45177.55208333334</v>
+        <v>45180.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>358.7</v>
+        <v>361.7</v>
       </c>
       <c r="I27" t="n">
         <v>361.3952357552074</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K27" t="n">
-        <v>5.36</v>
+        <v>4.56</v>
       </c>
       <c r="L27" t="n">
         <v>0.66</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>2.99</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>358.6</v>
+        <v>354.3</v>
       </c>
       <c r="I28" t="n">
         <v>355.1970706545023</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.86</v>
+        <v>-2.05</v>
       </c>
       <c r="L28" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="M28" t="n">
         <v>0.55</v>
       </c>
       <c r="N28" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.12</v>
       </c>
       <c r="O28" t="n">
         <v>0.89</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>3.28</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>352.2</v>
+        <v>355.7</v>
       </c>
       <c r="I29" t="n">
         <v>353.6526111042677</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>0.59</v>
+        <v>-0.4</v>
       </c>
       <c r="L29" t="n">
         <v>1.1</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>3.54</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45224.55208333334</v>
+        <v>45225.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>347</v>
+        <v>340.6</v>
       </c>
       <c r="I30" t="n">
         <v>344.5728118544899</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.45</v>
+        <v>-4.25</v>
       </c>
       <c r="L30" t="n">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="M30" t="n">
         <v>0.63</v>
       </c>
       <c r="N30" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="O30" t="n">
         <v>0.74</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>4.5</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>349.6</v>
+        <v>353.4</v>
       </c>
       <c r="I31" t="n">
         <v>352.5219883546975</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.64</v>
+        <v>-3.76</v>
       </c>
       <c r="L31" t="n">
-        <v>3.41</v>
+        <v>3.76</v>
       </c>
       <c r="M31" t="n">
         <v>0.95</v>
       </c>
       <c r="N31" t="n">
-        <v>0.99</v>
+        <v>1.37</v>
       </c>
       <c r="O31" t="n">
         <v>-2.48</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>3</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45296.38541666666</v>
+        <v>45296.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>370.9</v>
+        <v>369</v>
       </c>
       <c r="I32" t="n">
         <v>370.5231634637003</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>51</v>
+        <v>51.16666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>4.95</v>
+        <v>4.41</v>
       </c>
       <c r="L32" t="n">
         <v>1.9</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>3.29</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45356.55208333334</v>
+        <v>45357.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>343.6</v>
+        <v>352.3</v>
       </c>
       <c r="I33" t="n">
         <v>348.1555432116006</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>60</v>
+        <v>60.83333333333334</v>
       </c>
       <c r="K33" t="n">
-        <v>6.88</v>
+        <v>4.53</v>
       </c>
       <c r="L33" t="n">
         <v>0.87</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>4.83</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45384.55208333334</v>
+        <v>45385.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>351.3</v>
+        <v>347.2</v>
       </c>
       <c r="I34" t="n">
         <v>348.3793614656693</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.28</v>
+        <v>-1.45</v>
       </c>
       <c r="L34" t="n">
         <v>3.07</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>4.14</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45387.55208333334</v>
+        <v>45390.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>356.8</v>
+        <v>358.9</v>
       </c>
       <c r="I35" t="n">
         <v>358.3519573481369</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.76</v>
+        <v>-3.37</v>
       </c>
       <c r="L35" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="M35" t="n">
         <v>0.8100000000000001</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>3.56</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45406.55208333334</v>
+        <v>45407.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>368.6</v>
+        <v>328.8</v>
       </c>
       <c r="I36" t="n">
         <v>355.4214502960261</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K36" t="n">
-        <v>2.7</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>1.76</v>
+        <v>10.73</v>
       </c>
       <c r="M36" t="n">
-        <v>1.29</v>
+        <v>9.66</v>
       </c>
       <c r="N36" t="n">
-        <v>0.85</v>
+        <v>10.74</v>
       </c>
       <c r="O36" t="n">
         <v>0.11</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.23</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45420.38541666666</v>
+        <v>45420.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>329.1</v>
+        <v>329.6</v>
       </c>
       <c r="I37" t="n">
         <v>329.2229706740411</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.09</v>
+        <v>-0.24</v>
       </c>
       <c r="L37" t="n">
         <v>3.28</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>5.32</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>344.1</v>
+        <v>326.8</v>
       </c>
       <c r="I38" t="n">
         <v>331.9660152624843</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>4.4</v>
+        <v>-0.85</v>
       </c>
       <c r="L38" t="n">
-        <v>1.94</v>
+        <v>2.76</v>
       </c>
       <c r="M38" t="n">
-        <v>0.62</v>
+        <v>1.02</v>
       </c>
       <c r="N38" t="n">
-        <v>1.16</v>
+        <v>4.45</v>
       </c>
       <c r="O38" t="n">
         <v>0.24</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>7.63</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I39" t="n">
         <v>347.4994256552178</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.88</v>
+        <v>-6.49</v>
       </c>
       <c r="L39" t="n">
-        <v>6.4</v>
+        <v>7.04</v>
       </c>
       <c r="M39" t="n">
         <v>1.13</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>6.15</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45474.55208333334</v>
+        <v>45475.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>360.9</v>
+        <v>348.9</v>
       </c>
       <c r="I40" t="n">
         <v>350.0967247629329</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K40" t="n">
-        <v>3.71</v>
+        <v>0.26</v>
       </c>
       <c r="L40" t="n">
         <v>2.13</v>
@@ -2721,7 +3200,7 @@
         <v>0.76</v>
       </c>
       <c r="N40" t="n">
-        <v>1.21</v>
+        <v>2.19</v>
       </c>
       <c r="O40" t="n">
         <v>1.3</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.16</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45478.55208333334</v>
+        <v>45481.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>368.9</v>
+        <v>369.6</v>
       </c>
       <c r="I41" t="n">
         <v>369.4392454452621</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.73</v>
+        <v>-5.93</v>
       </c>
       <c r="L41" t="n">
         <v>6.51</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.65</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45492.55208333334</v>
+        <v>45495.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>362.4</v>
+        <v>352.1</v>
       </c>
       <c r="I42" t="n">
         <v>355.7784654105861</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.95</v>
+        <v>-4.73</v>
       </c>
       <c r="L42" t="n">
-        <v>2.98</v>
+        <v>4.98</v>
       </c>
       <c r="M42" t="n">
         <v>0.11</v>
       </c>
       <c r="N42" t="n">
-        <v>1.85</v>
+        <v>2.73</v>
       </c>
       <c r="O42" t="n">
         <v>0.62</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.18</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45526.38541666666</v>
+        <v>45526.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>361.9</v>
+        <v>364.2</v>
       </c>
       <c r="I43" t="n">
         <v>362.8088928660703</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.78</v>
+        <v>-3.44</v>
       </c>
       <c r="L43" t="n">
         <v>3.95</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>3.61</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45562.55208333334</v>
+        <v>45565.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>375.2</v>
+        <v>369.1</v>
       </c>
       <c r="I44" t="n">
         <v>374.0448191284966</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>36</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K44" t="n">
-        <v>3.02</v>
+        <v>1.35</v>
       </c>
       <c r="L44" t="n">
         <v>3.54</v>
       </c>
       <c r="M44" t="n">
-        <v>0.78</v>
+        <v>1.04</v>
       </c>
       <c r="N44" t="n">
         <v>1.44</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>4.73</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45576.55208333334</v>
+        <v>45579.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>376.9</v>
+        <v>382.4</v>
       </c>
       <c r="I45" t="n">
         <v>377.3450394314402</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.11</v>
+        <v>-3.6</v>
       </c>
       <c r="L45" t="n">
-        <v>2.6</v>
+        <v>3.82</v>
       </c>
       <c r="M45" t="n">
         <v>0.28</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>5.32</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45583.55208333334</v>
+        <v>45586.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>374.4</v>
+        <v>355.7</v>
       </c>
       <c r="I46" t="n">
         <v>365.233920199516</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.09</v>
+        <v>-6.98</v>
       </c>
       <c r="L46" t="n">
-        <v>3.35</v>
+        <v>9.26</v>
       </c>
       <c r="M46" t="n">
-        <v>0.61</v>
+        <v>1.18</v>
       </c>
       <c r="N46" t="n">
-        <v>1.35</v>
+        <v>4.78</v>
       </c>
       <c r="O46" t="n">
         <v>1.51</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>6.81</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>352.4</v>
+        <v>354.2</v>
       </c>
       <c r="I47" t="n">
         <v>352.5224496641744</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K47" t="n">
-        <v>0.93</v>
+        <v>0.42</v>
       </c>
       <c r="L47" t="n">
         <v>4.3</v>
       </c>
       <c r="M47" t="n">
-        <v>0.64</v>
+        <v>1.14</v>
       </c>
       <c r="N47" t="n">
         <v>1.74</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>3.41</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45649.38541666666</v>
+        <v>45649.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>350</v>
+        <v>348.4</v>
       </c>
       <c r="I48" t="n">
         <v>349.2657757193807</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.19</v>
+        <v>-1.64</v>
       </c>
       <c r="L48" t="n">
         <v>2.12</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>3.71</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>357.6</v>
+        <v>365.2</v>
       </c>
       <c r="I49" t="n">
         <v>360.5601473983449</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.64</v>
+        <v>-4.82</v>
       </c>
       <c r="L49" t="n">
-        <v>3.16</v>
+        <v>5.4</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="N49" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="O49" t="n">
         <v>-0.37</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>4.43</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>354.1</v>
+        <v>353</v>
       </c>
       <c r="I50" t="n">
         <v>353.8198659255362</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.04</v>
+        <v>-3.34</v>
       </c>
       <c r="L50" t="n">
-        <v>3.07</v>
+        <v>3.48</v>
       </c>
       <c r="M50" t="n">
         <v>0.79</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>4.48</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>357.6</v>
+        <v>362.8</v>
       </c>
       <c r="I51" t="n">
         <v>361.282742175495</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.3</v>
+        <v>-2.78</v>
       </c>
       <c r="L51" t="n">
-        <v>2.46</v>
+        <v>2.83</v>
       </c>
       <c r="M51" t="n">
         <v>0.55</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.88</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45716.38541666666</v>
+        <v>45716.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>382</v>
+        <v>379.7</v>
       </c>
       <c r="I52" t="n">
         <v>380.510833993717</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>5.29</v>
+        <v>4.66</v>
       </c>
       <c r="L52" t="n">
         <v>3.61</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>4.2</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45727.55208333334</v>
+        <v>45728.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>387.6</v>
+        <v>396.4</v>
       </c>
       <c r="I53" t="n">
         <v>394.8723990042844</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.08</v>
+        <v>-4.4</v>
       </c>
       <c r="L53" t="n">
-        <v>2.9</v>
+        <v>5.21</v>
       </c>
       <c r="M53" t="n">
         <v>0.37</v>
       </c>
       <c r="N53" t="n">
-        <v>1.36</v>
+        <v>2.17</v>
       </c>
       <c r="O53" t="n">
         <v>-2.24</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>4.66</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>426.4</v>
+        <v>403.2</v>
       </c>
       <c r="I54" t="n">
         <v>419.4345027178189</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K54" t="n">
-        <v>7.57</v>
+        <v>1.72</v>
       </c>
       <c r="L54" t="n">
         <v>2.22</v>
       </c>
       <c r="M54" t="n">
-        <v>0.72</v>
+        <v>5.32</v>
       </c>
       <c r="N54" t="n">
-        <v>1.36</v>
+        <v>4.13</v>
       </c>
       <c r="O54" t="n">
         <v>2.17</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>6.71</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45763.55208333334</v>
+        <v>45764.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>424.3</v>
+        <v>435.6</v>
       </c>
       <c r="I55" t="n">
         <v>427.7016932639884</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.23</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>6.72</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M55" t="n">
         <v>1.44</v>
       </c>
       <c r="N55" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="O55" t="n">
         <v>-4.13</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>7.1</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45779.55208333334</v>
+        <v>45782.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>436</v>
+        <v>415.5</v>
       </c>
       <c r="I56" t="n">
         <v>430.7352700651014</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K56" t="n">
-        <v>0.09</v>
+        <v>-4.61</v>
       </c>
       <c r="L56" t="n">
-        <v>3.7</v>
+        <v>5.51</v>
       </c>
       <c r="M56" t="n">
-        <v>0.36</v>
+        <v>3.44</v>
       </c>
       <c r="N56" t="n">
-        <v>1.5</v>
+        <v>4.36</v>
       </c>
       <c r="O56" t="n">
         <v>2.99</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.11</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45814.55208333334</v>
+        <v>45817.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>414.4</v>
+        <v>428.1</v>
       </c>
       <c r="I57" t="n">
         <v>420.4562265290759</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K57" t="n">
-        <v>0.26</v>
+        <v>-3.03</v>
       </c>
       <c r="L57" t="n">
         <v>4.14</v>
       </c>
       <c r="M57" t="n">
-        <v>1.31</v>
+        <v>1.88</v>
       </c>
       <c r="N57" t="n">
-        <v>1.73</v>
+        <v>3.28</v>
       </c>
       <c r="O57" t="n">
         <v>-4.36</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.92</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45840.55208333334</v>
+        <v>45841.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>432.9</v>
+        <v>425.9</v>
       </c>
       <c r="I58" t="n">
         <v>428.2535492243106</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K58" t="n">
-        <v>1.12</v>
+        <v>-0.51</v>
       </c>
       <c r="L58" t="n">
         <v>3.2</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>3.83</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45845.55208333334</v>
+        <v>45846.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>430</v>
+        <v>444.6</v>
       </c>
       <c r="I59" t="n">
         <v>438.5505609616104</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.96</v>
+        <v>-4.39</v>
       </c>
       <c r="L59" t="n">
-        <v>1.29</v>
+        <v>5.26</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="N59" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="O59" t="n">
         <v>-1.82</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>4.59</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45855.55208333334</v>
+        <v>45856.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>434.6</v>
+        <v>429.9</v>
       </c>
       <c r="I60" t="n">
         <v>431.7665634088007</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.25</v>
+        <v>-3.31</v>
       </c>
       <c r="L60" t="n">
-        <v>3.01</v>
+        <v>4.14</v>
       </c>
       <c r="M60" t="n">
         <v>0.68</v>
       </c>
       <c r="N60" t="n">
-        <v>0.84</v>
+        <v>1.89</v>
       </c>
       <c r="O60" t="n">
         <v>3.3</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>3.48</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45915.55208333334</v>
+        <v>45916.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>394</v>
+        <v>404.3</v>
       </c>
       <c r="I61" t="n">
         <v>399.5212199798914</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K61" t="n">
-        <v>8.35</v>
+        <v>5.95</v>
       </c>
       <c r="L61" t="n">
         <v>1.42</v>
@@ -3918,7 +4649,7 @@
         <v>1.25</v>
       </c>
       <c r="N61" t="n">
-        <v>1.52</v>
+        <v>2.72</v>
       </c>
       <c r="O61" t="n">
         <v>-1.89</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>4.13</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>400.4</v>
+        <v>398.7</v>
       </c>
       <c r="I62" t="n">
         <v>399.2947757784227</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.96</v>
+        <v>-1.39</v>
       </c>
       <c r="L62" t="n">
         <v>2.4</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>2.92</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45930.55208333334</v>
+        <v>45931.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>399.2</v>
+        <v>411.2</v>
       </c>
       <c r="I63" t="n">
         <v>409.2777754272867</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.13</v>
+        <v>-3.14</v>
       </c>
       <c r="L63" t="n">
-        <v>1.08</v>
+        <v>3.16</v>
       </c>
       <c r="M63" t="n">
         <v>1.11</v>
       </c>
       <c r="N63" t="n">
-        <v>0.71</v>
+        <v>3.58</v>
       </c>
       <c r="O63" t="n">
         <v>-1.07</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.42</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45957.38541666666</v>
+        <v>45957.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>431.2</v>
+        <v>429.9</v>
       </c>
       <c r="I64" t="n">
         <v>430.6704711780968</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>4.86</v>
+        <v>4.55</v>
       </c>
       <c r="L64" t="n">
         <v>3.4</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>4.83</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45989.55208333334</v>
+        <v>45992.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>425</v>
+        <v>430.6</v>
       </c>
       <c r="I65" t="n">
         <v>426.4757484248086</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>32</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K65" t="n">
-        <v>1.14</v>
+        <v>-0.16</v>
       </c>
       <c r="L65" t="n">
         <v>1.16</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>3.7</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46027.55208333334</v>
+        <v>46028.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>438.5</v>
+        <v>428.7</v>
       </c>
       <c r="I66" t="n">
         <v>431.82577554211</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K66" t="n">
-        <v>1.83</v>
+        <v>-0.44</v>
       </c>
       <c r="L66" t="n">
         <v>2.04</v>
@@ -4203,7 +4994,7 @@
         <v>0.48</v>
       </c>
       <c r="N66" t="n">
-        <v>1.29</v>
+        <v>2.28</v>
       </c>
       <c r="O66" t="n">
         <v>1.06</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.69</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46062.55208333334</v>
+        <v>46063.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>427.1</v>
+        <v>432.9</v>
       </c>
       <c r="I67" t="n">
         <v>427.7349049231759</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K67" t="n">
-        <v>0.37</v>
+        <v>-0.98</v>
       </c>
       <c r="L67" t="n">
         <v>3.94</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,25 +5111,25 @@
         <v>5.64</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>416.05</v>
+        <v>409.85</v>
       </c>
       <c r="I68" t="n">
         <v>413.4110666764641</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.89</v>
+        <v>-5.32</v>
       </c>
       <c r="L68" t="n">
-        <v>4.26</v>
+        <v>5.96</v>
       </c>
       <c r="M68" t="n">
-        <v>0.91</v>
+        <v>1.45</v>
       </c>
       <c r="N68" t="n">
         <v>2.02</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>4.32</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>363.1</v>
+        <v>377.35</v>
       </c>
       <c r="I69" t="n">
         <v>372.606715139235</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K69" t="n">
-        <v>11.41</v>
+        <v>7.93</v>
       </c>
       <c r="L69" t="n">
         <v>1.16</v>
       </c>
       <c r="M69" t="n">
-        <v>3.06</v>
+        <v>3.83</v>
       </c>
       <c r="N69" t="n">
-        <v>3.1</v>
+        <v>4.52</v>
       </c>
       <c r="O69" t="n">
         <v>-1.17</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.14</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46147.55208333334</v>
+        <v>46148.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>371.25</v>
+        <v>365.8</v>
       </c>
       <c r="I70" t="n">
         <v>366.2143809070508</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.62</v>
+        <v>-3.06</v>
       </c>
       <c r="L70" t="n">
         <v>3.8</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>6.88</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46160.38541666666</v>
+        <v>46160.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>389.9</v>
+        <v>391.45</v>
       </c>
       <c r="I71" t="n">
         <v>390.9546967181956</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.59</v>
+        <v>-7.01</v>
       </c>
       <c r="L71" t="n">
         <v>7.52</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>5.34</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46202.55208333334</v>
+        <v>46203.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>397</v>
+        <v>392.85</v>
       </c>
       <c r="I72" t="n">
         <v>396.4054465915758</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K72" t="n">
-        <v>1.42</v>
+        <v>0.36</v>
       </c>
       <c r="L72" t="n">
         <v>4.92</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>4.6</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46220.38541666666</v>
+        <v>46220.55208333334</v>
       </c>
       <c r="H73" t="n">
-        <v>385.55</v>
+        <v>390.7</v>
       </c>
       <c r="I73" t="n">
         <v>387.3898787893395</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K73" t="n">
-        <v>1.86</v>
+        <v>0.55</v>
       </c>
       <c r="L73" t="n">
         <v>3.09</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>5.2</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46288.55208333334</v>
+        <v>46289.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>413</v>
+        <v>408.45</v>
       </c>
       <c r="I74" t="n">
         <v>411.5449082482133</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>68</v>
+        <v>68.83333333333333</v>
       </c>
       <c r="K74" t="n">
-        <v>5.71</v>
+        <v>4.54</v>
       </c>
       <c r="L74" t="n">
         <v>3.74</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>3.02</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46294.55208333334</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>406.85</v>
+        <v>417.2</v>
       </c>
       <c r="I75" t="n">
         <v>413.441465199834</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>0.39</v>
+        <v>-2.14</v>
       </c>
       <c r="L75" t="n">
-        <v>0.38</v>
+        <v>2.62</v>
       </c>
       <c r="M75" t="n">
         <v>0.41</v>
       </c>
       <c r="N75" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="O75" t="n">
         <v>-1.88</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>5.49</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46318.38541666666</v>
+        <v>46318.55208333334</v>
       </c>
       <c r="H76" t="n">
-        <v>430.4</v>
+        <v>429</v>
       </c>
       <c r="I76" t="n">
         <v>429.8299586896267</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K76" t="n">
-        <v>3.16</v>
+        <v>2.83</v>
       </c>
       <c r="L76" t="n">
         <v>2.7</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,14 @@
       <c r="Q77" t="n">
         <v>7</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6935,7 +7866,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="6">
@@ -6945,7 +7876,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -6955,7 +7886,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="8">
@@ -6965,7 +7896,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6975,7 +7906,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.1</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="10">
@@ -6985,7 +7916,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44.8</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="11">
@@ -7025,7 +7956,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.34</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="15">
@@ -7035,7 +7966,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.82</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="16">
@@ -7045,7 +7976,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.14</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="17">
@@ -7055,7 +7986,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12.61</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="18">
@@ -7065,7 +7996,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
@@ -7075,7 +8006,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.11</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="20">
@@ -7085,7 +8016,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.07</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="21">
@@ -7095,7 +8026,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.52</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="22">
@@ -7105,7 +8036,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -7115,7 +8046,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -7125,7 +8056,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="25">
@@ -7135,7 +8066,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.55</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="26">
@@ -7145,7 +8076,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.2</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="27">
@@ -7155,7 +8086,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.26</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="28">
@@ -7165,7 +8096,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
